--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{122EFD3D-4AE5-4D15-B7F5-982EE4D3EC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11664" yWindow="264" windowWidth="10872" windowHeight="8616" xr2:uid="{DDD1AAAD-7A7A-4442-9F29-C8E316967F40}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DDD1AAAD-7A7A-4442-9F29-C8E316967F40}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
